--- a/JsonConverter/ExcelFiles/OO_Choice.xlsx
+++ b/JsonConverter/ExcelFiles/OO_Choice.xlsx
@@ -2,17 +2,21 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="450" yWindow="500" windowWidth="27760" windowHeight="10800" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DNTable_Choice" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="9">
     <font>
       <name val="Arial"/>
       <color rgb="FF000000"/>
@@ -20,51 +24,53 @@
     </font>
     <font>
       <name val="&quot;맑은 고딕&quot;"/>
+      <charset val="129"/>
+      <family val="3"/>
       <color rgb="FF000000"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
-      <color theme="1"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Arial"/>
+      <name val="돋움"/>
+      <charset val="129"/>
+      <family val="3"/>
       <color rgb="FF000000"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="FF000000"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="돋움"/>
-      <color theme="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="돋움"/>
-      <color rgb="FF000000"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
+      <family val="2"/>
       <b val="1"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
+      <family val="2"/>
       <b val="1"/>
       <color rgb="FFFFFFFF"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="돋움"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="?? ??"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="13">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -78,37 +84,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD9EAF7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCE4D6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE2F0D9"/>
+        <fgColor theme="7" tint="0.7999511703848384"/>
+        <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
@@ -126,9 +103,20 @@
         <fgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
-    <border/>
+  <borders count="3">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color indexed="64"/>
@@ -142,20 +130,7 @@
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -170,172 +145,54 @@
       <bottom style="thin">
         <color rgb="FFBFBFBF"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="표준" xfId="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -549,6 +406,8 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -558,253 +417,247 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="17" defaultRowHeight="15"/>
+  <dimension ref="A1:N8"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="17" defaultRowHeight="12.5"/>
   <cols>
-    <col width="28.75" customWidth="1" style="2" min="1" max="1"/>
-    <col width="23.75" customWidth="1" style="2" min="2" max="2"/>
-    <col width="53.75" customWidth="1" min="3" max="3"/>
-    <col width="13.75" customWidth="1" min="4" max="4"/>
-    <col width="13.75" customWidth="1" style="2" min="5" max="5"/>
-    <col width="23.75" customWidth="1" style="2" min="6" max="6"/>
-    <col width="23.75" customWidth="1" style="2" min="7" max="7"/>
-    <col width="23.75" customWidth="1" min="8" max="8"/>
-    <col width="23.75" customWidth="1" min="9" max="9"/>
-    <col width="23.75" customWidth="1" min="10" max="10"/>
-    <col width="23.75" customWidth="1" min="11" max="11"/>
-    <col width="23.75" customWidth="1" min="12" max="12"/>
-    <col width="23.75" customWidth="1" min="13" max="13"/>
-    <col width="52.5" customWidth="1" min="14" max="14"/>
+    <col width="28.7265625" customWidth="1" style="1" min="1" max="1"/>
+    <col width="23.7265625" customWidth="1" style="1" min="2" max="2"/>
+    <col width="53.7265625" customWidth="1" min="3" max="3"/>
+    <col width="13.7265625" customWidth="1" min="4" max="4"/>
+    <col width="13.7265625" customWidth="1" style="1" min="5" max="5"/>
+    <col width="23.7265625" customWidth="1" style="1" min="6" max="7"/>
+    <col width="23.7265625" customWidth="1" min="8" max="13"/>
+    <col width="52.453125" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="31.5" customHeight="1">
-      <c r="A1" s="54" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>선택지 ID</t>
         </is>
       </c>
-      <c r="B1" s="54" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>화자 캐릭터 ID</t>
         </is>
       </c>
-      <c r="C1" s="54" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>질문 문장</t>
         </is>
       </c>
-      <c r="D1" s="54" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>선택 방식</t>
         </is>
       </c>
-      <c r="E1" s="54" t="inlineStr">
+      <c r="E1" s="4" t="inlineStr">
         <is>
           <t>선택지 개수</t>
         </is>
       </c>
-      <c r="F1" s="54" t="inlineStr">
+      <c r="F1" s="4" t="inlineStr">
         <is>
           <t>입력 키 목록(| 구분)</t>
         </is>
       </c>
-      <c r="G1" s="54" t="inlineStr">
+      <c r="G1" s="4" t="inlineStr">
         <is>
           <t>선택지 표시 문구 목록(| 구분)</t>
         </is>
       </c>
-      <c r="H1" s="54" t="inlineStr">
+      <c r="H1" s="4" t="inlineStr">
         <is>
           <t>결과 타입 목록(| 구분)</t>
         </is>
       </c>
-      <c r="I1" s="54" t="inlineStr">
+      <c r="I1" s="4" t="inlineStr">
         <is>
           <t>결과 값 목록(| 구분)</t>
         </is>
       </c>
-      <c r="J1" s="54" t="inlineStr">
+      <c r="J1" s="4" t="inlineStr">
         <is>
           <t>결과 수량 목록(| 구분)</t>
         </is>
       </c>
-      <c r="K1" s="54" t="inlineStr">
+      <c r="K1" s="4" t="inlineStr">
         <is>
           <t>다음 대사 ID 목록(| 구분)</t>
         </is>
       </c>
-      <c r="L1" s="54" t="inlineStr">
+      <c r="L1" s="4" t="inlineStr">
         <is>
           <t>다음 선택지 ID 목록(| 구분)</t>
         </is>
       </c>
-      <c r="M1" s="54" t="inlineStr">
+      <c r="M1" s="4" t="inlineStr">
         <is>
           <t>갱신 퀘스트 ID 목록(| 구분)</t>
         </is>
       </c>
-      <c r="N1" s="54" t="inlineStr">
+      <c r="N1" s="4" t="inlineStr">
         <is>
           <t>메모</t>
         </is>
       </c>
     </row>
     <row r="2" ht="31.5" customHeight="1">
-      <c r="A2" s="55" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="B2" s="55" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="C2" s="55" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D2" s="55" t="inlineStr">
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="E2" s="55" t="inlineStr">
+      <c r="E2" s="5" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F2" s="55" t="inlineStr">
+      <c r="F2" s="5" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="G2" s="56" t="inlineStr">
+      <c r="G2" s="6" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="H2" s="56" t="inlineStr">
+      <c r="H2" s="6" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="I2" s="57" t="inlineStr">
+      <c r="I2" s="7" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="J2" s="57" t="inlineStr">
+      <c r="J2" s="7" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="K2" s="57" t="inlineStr">
+      <c r="K2" s="7" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="L2" s="57" t="inlineStr">
+      <c r="L2" s="7" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="M2" s="57" t="inlineStr">
+      <c r="M2" s="7" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N2" s="57" t="inlineStr">
+      <c r="N2" s="7" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="31.5" customFormat="1" customHeight="1" s="11">
-      <c r="A3" s="58" t="inlineStr">
+    <row r="3" ht="31.5" customFormat="1" customHeight="1" s="3">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>Id</t>
         </is>
       </c>
-      <c r="B3" s="58" t="inlineStr">
+      <c r="B3" s="8" t="inlineStr">
         <is>
           <t>SpeakerId</t>
         </is>
       </c>
-      <c r="C3" s="58" t="inlineStr">
+      <c r="C3" s="8" t="inlineStr">
         <is>
           <t>PromptText</t>
         </is>
       </c>
-      <c r="D3" s="58" t="inlineStr">
+      <c r="D3" s="8" t="inlineStr">
         <is>
           <t>ChoiceMode</t>
         </is>
       </c>
-      <c r="E3" s="58" t="inlineStr">
+      <c r="E3" s="8" t="inlineStr">
         <is>
           <t>OptionCount</t>
         </is>
       </c>
-      <c r="F3" s="58" t="inlineStr">
+      <c r="F3" s="8" t="inlineStr">
         <is>
           <t>OptionKeyList</t>
         </is>
       </c>
-      <c r="G3" s="58" t="inlineStr">
+      <c r="G3" s="8" t="inlineStr">
         <is>
           <t>OptionTextList</t>
         </is>
       </c>
-      <c r="H3" s="58" t="inlineStr">
+      <c r="H3" s="8" t="inlineStr">
         <is>
           <t>ResultTypeList</t>
         </is>
       </c>
-      <c r="I3" s="59" t="inlineStr">
+      <c r="I3" s="9" t="inlineStr">
         <is>
           <t>ResultValueList</t>
         </is>
       </c>
-      <c r="J3" s="59" t="inlineStr">
+      <c r="J3" s="9" t="inlineStr">
         <is>
           <t>ResultCountList</t>
         </is>
       </c>
-      <c r="K3" s="59" t="inlineStr">
+      <c r="K3" s="9" t="inlineStr">
         <is>
           <t>NextDialogueIdList</t>
         </is>
       </c>
-      <c r="L3" s="59" t="inlineStr">
+      <c r="L3" s="9" t="inlineStr">
         <is>
           <t>NextChoiceIdList</t>
         </is>
       </c>
-      <c r="M3" s="59" t="inlineStr">
+      <c r="M3" s="9" t="inlineStr">
         <is>
           <t>StageQuestIdList</t>
         </is>
       </c>
-      <c r="N3" s="59" t="inlineStr">
+      <c r="N3" s="9" t="inlineStr">
         <is>
           <t>Memo</t>
         </is>
       </c>
     </row>
     <row r="4" ht="31.5" customHeight="1">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>Choice_Stage1_CartPumpkin_01</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>character_narrator_01</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="11" t="inlineStr">
         <is>
           <t>탐관오리처럼 탐욕스럽게 생긴 호박들입니다. 호박을 수확하시겠습니까?</t>
         </is>
@@ -863,10 +716,286 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="15.75" customHeight="1"/>
-    <row r="6" ht="15.75" customHeight="1"/>
-    <row r="7" ht="15.75" customHeight="1"/>
-    <row r="8" ht="15.75" customHeight="1"/>
+    <row r="5" ht="15.75" customHeight="1">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>Choice_Stage3_SungunQuest_01</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>character_narrator_01</t>
+        </is>
+      </c>
+      <c r="C5" s="15" t="inlineStr">
+        <is>
+          <t>떡과 꿀을 조합해 꿀떡을 만드시겠습니까?</t>
+        </is>
+      </c>
+      <c r="D5" s="15" t="inlineStr">
+        <is>
+          <t>YesNo</t>
+        </is>
+      </c>
+      <c r="E5" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" s="14" t="inlineStr">
+        <is>
+          <t>Y|N</t>
+        </is>
+      </c>
+      <c r="G5" s="15" t="inlineStr">
+        <is>
+          <t>예|아니오</t>
+        </is>
+      </c>
+      <c r="H5" s="15" t="inlineStr">
+        <is>
+          <t>MakeItem|Close</t>
+        </is>
+      </c>
+      <c r="I5" s="15" t="inlineStr">
+        <is>
+          <t>OO_HoneyKoreanCake_1|</t>
+        </is>
+      </c>
+      <c r="J5" s="15" t="inlineStr">
+        <is>
+          <t>1|0</t>
+        </is>
+      </c>
+      <c r="K5" s="15" t="inlineStr">
+        <is>
+          <t>|</t>
+        </is>
+      </c>
+      <c r="L5" s="15" t="inlineStr">
+        <is>
+          <t>|</t>
+        </is>
+      </c>
+      <c r="M5" s="15" t="inlineStr">
+        <is>
+          <t>|</t>
+        </is>
+      </c>
+      <c r="N5" s="15" t="inlineStr">
+        <is>
+          <t>필요 재료: OO_KoreanCake_1 1개 + Ing_Honey_01 1개. 예 선택 시 재료를 소비하고 꿀떡 1개를 추가한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="15.75" customHeight="1">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>Choice_Stage3_SungunQuest_02</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>character_narrator_01</t>
+        </is>
+      </c>
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t>꿀 없이 떡만 산군에게 주시겠습니까?</t>
+        </is>
+      </c>
+      <c r="D6" s="15" t="inlineStr">
+        <is>
+          <t>YesNo</t>
+        </is>
+      </c>
+      <c r="E6" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" s="15" t="inlineStr">
+        <is>
+          <t>Y|N</t>
+        </is>
+      </c>
+      <c r="G6" s="15" t="inlineStr">
+        <is>
+          <t>예|아니오</t>
+        </is>
+      </c>
+      <c r="H6" s="15" t="inlineStr">
+        <is>
+          <t>BadEnd|Close</t>
+        </is>
+      </c>
+      <c r="I6" s="15" t="inlineStr">
+        <is>
+          <t>Choice_Stage3_SungunQuest_04|</t>
+        </is>
+      </c>
+      <c r="J6" s="15" t="inlineStr">
+        <is>
+          <t>0|0</t>
+        </is>
+      </c>
+      <c r="K6" s="15" t="inlineStr">
+        <is>
+          <t>|</t>
+        </is>
+      </c>
+      <c r="L6" s="15" t="inlineStr">
+        <is>
+          <t>Choice_Stage3_SungunQuest_04|</t>
+        </is>
+      </c>
+      <c r="M6" s="15" t="inlineStr">
+        <is>
+          <t>|</t>
+        </is>
+      </c>
+      <c r="N6" s="15" t="inlineStr">
+        <is>
+          <t>떡만 있을 때 EncounterGroup 복귀 즉시 표시. 예 선택 시 산군 공격/피 효과/YOU DIE 후 재시도 선택지로 이동.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="15.75" customHeight="1">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>Choice_Stage3_SungunQuest_03</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>character_narrator_01</t>
+        </is>
+      </c>
+      <c r="C7" s="15" t="inlineStr">
+        <is>
+          <t>완성한 꿀떡을 산군에게 주시겠습니까?</t>
+        </is>
+      </c>
+      <c r="D7" s="15" t="inlineStr">
+        <is>
+          <t>YesNo</t>
+        </is>
+      </c>
+      <c r="E7" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" s="15" t="inlineStr">
+        <is>
+          <t>Y|N</t>
+        </is>
+      </c>
+      <c r="G7" s="15" t="inlineStr">
+        <is>
+          <t>예|아니오</t>
+        </is>
+      </c>
+      <c r="H7" s="15" t="inlineStr">
+        <is>
+          <t>CompleteQuest|Close</t>
+        </is>
+      </c>
+      <c r="I7" s="15" t="inlineStr">
+        <is>
+          <t>OO_HoneyKoreanCake_1|</t>
+        </is>
+      </c>
+      <c r="J7" s="15" t="inlineStr">
+        <is>
+          <t>1|0</t>
+        </is>
+      </c>
+      <c r="K7" s="15" t="inlineStr">
+        <is>
+          <t>character_Sangun_04|</t>
+        </is>
+      </c>
+      <c r="L7" s="15" t="inlineStr">
+        <is>
+          <t>|</t>
+        </is>
+      </c>
+      <c r="M7" s="15" t="inlineStr">
+        <is>
+          <t>Stage3__Quest_01|</t>
+        </is>
+      </c>
+      <c r="N7" s="15" t="inlineStr">
+        <is>
+          <t>꿀떡이 있을 때 EncounterGroup 복귀 즉시 표시. 예 선택 시 꿀떡을 소비하고 Stage3 퀘스트 완료 처리.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="15.75" customHeight="1">
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>Choice_Stage3_SungunQuest_04</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>character_narrator_01</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="inlineStr">
+        <is>
+          <t>전 장면으로 돌아가겠습니까?</t>
+        </is>
+      </c>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t>YesNo</t>
+        </is>
+      </c>
+      <c r="E8" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" s="15" t="inlineStr">
+        <is>
+          <t>Y|N</t>
+        </is>
+      </c>
+      <c r="G8" s="15" t="inlineStr">
+        <is>
+          <t>예|아니오</t>
+        </is>
+      </c>
+      <c r="H8" s="15" t="inlineStr">
+        <is>
+          <t>ReturnPrevious|LoadGroup</t>
+        </is>
+      </c>
+      <c r="I8" s="15" t="inlineStr">
+        <is>
+          <t>EncounterGroup|MainMenuGroup</t>
+        </is>
+      </c>
+      <c r="J8" s="15" t="inlineStr">
+        <is>
+          <t>0|0</t>
+        </is>
+      </c>
+      <c r="K8" s="15" t="inlineStr">
+        <is>
+          <t>|</t>
+        </is>
+      </c>
+      <c r="L8" s="15" t="inlineStr">
+        <is>
+          <t>|</t>
+        </is>
+      </c>
+      <c r="M8" s="15" t="inlineStr">
+        <is>
+          <t>|</t>
+        </is>
+      </c>
+      <c r="N8" s="15" t="inlineStr">
+        <is>
+          <t>YOU DIE 이후 표시. 예는 EncounterGroup 재시작, 아니오는 메인 메뉴 이동.</t>
+        </is>
+      </c>
+    </row>
     <row r="9" ht="15.75" customHeight="1"/>
     <row r="10" ht="15.75" customHeight="1"/>
     <row r="11" ht="15.75" customHeight="1"/>

--- a/JsonConverter/ExcelFiles/OO_Choice.xlsx
+++ b/JsonConverter/ExcelFiles/OO_Choice.xlsx
@@ -1,78 +1,272 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="450" yWindow="500" windowWidth="27760" windowHeight="10800" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="450" yWindow="500" windowWidth="27760" windowHeight="10800"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DNTable_Choice" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="DNTable_Choice" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="65">
+  <si>
+    <t>선택지 ID</t>
+  </si>
+  <si>
+    <t>화자 캐릭터 ID</t>
+  </si>
+  <si>
+    <t>질문 문장</t>
+  </si>
+  <si>
+    <t>선택 방식</t>
+  </si>
+  <si>
+    <t>선택지 개수</t>
+  </si>
+  <si>
+    <t>입력 키 목록(| 구분)</t>
+  </si>
+  <si>
+    <t>선택지 표시 문구 목록(| 구분)</t>
+  </si>
+  <si>
+    <t>결과 타입 목록(| 구분)</t>
+  </si>
+  <si>
+    <t>결과 값 목록(| 구분)</t>
+  </si>
+  <si>
+    <t>결과 수량 목록(| 구분)</t>
+  </si>
+  <si>
+    <t>다음 대사 ID 목록(| 구분)</t>
+  </si>
+  <si>
+    <t>다음 선택지 ID 목록(| 구분)</t>
+  </si>
+  <si>
+    <t>갱신 퀘스트 ID 목록(| 구분)</t>
+  </si>
+  <si>
+    <t>메모</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>Id</t>
+  </si>
+  <si>
+    <t>SpeakerId</t>
+  </si>
+  <si>
+    <t>PromptText</t>
+  </si>
+  <si>
+    <t>ChoiceMode</t>
+  </si>
+  <si>
+    <t>OptionCount</t>
+  </si>
+  <si>
+    <t>OptionKeyList</t>
+  </si>
+  <si>
+    <t>OptionTextList</t>
+  </si>
+  <si>
+    <t>ResultTypeList</t>
+  </si>
+  <si>
+    <t>ResultValueList</t>
+  </si>
+  <si>
+    <t>ResultCountList</t>
+  </si>
+  <si>
+    <t>NextDialogueIdList</t>
+  </si>
+  <si>
+    <t>NextChoiceIdList</t>
+  </si>
+  <si>
+    <t>StageQuestIdList</t>
+  </si>
+  <si>
+    <t>Memo</t>
+  </si>
+  <si>
+    <t>Choice_Stage1_CartPumpkin_01</t>
+  </si>
+  <si>
+    <t>character_narrator_01</t>
+  </si>
+  <si>
+    <t>탐관오리처럼 탐욕스럽게 생긴 호박들입니다. 호박을 수확하시겠습니까?</t>
+  </si>
+  <si>
+    <t>YesNo</t>
+  </si>
+  <si>
+    <t>Y|N</t>
+  </si>
+  <si>
+    <t>예|아니오</t>
+  </si>
+  <si>
+    <t>AddItem|Close</t>
+  </si>
+  <si>
+    <t>Ing_Pumpkin_01|</t>
+  </si>
+  <si>
+    <t>10|0</t>
+  </si>
+  <si>
+    <t>|</t>
+  </si>
+  <si>
+    <t>Stage1_Quest_03|</t>
+  </si>
+  <si>
+    <t>Stage1 Cart choice data</t>
+  </si>
+  <si>
+    <t>MakeItem|Close</t>
+  </si>
+  <si>
+    <t>OO_HoneyKoreanCake_1|</t>
+  </si>
+  <si>
+    <t>1|0</t>
+  </si>
+  <si>
+    <t>필요 재료: OO_KoreanCake_1 1개 + Ing_Honey_01 1개. 예 선택 시 재료를 소비하고 꿀떡 1개를 추가한다.</t>
+  </si>
+  <si>
+    <t>Choice_Stage3_SungunQuest_02</t>
+  </si>
+  <si>
+    <t>BadEnd|Close</t>
+  </si>
+  <si>
+    <t>Choice_Stage3_SungunQuest_04|</t>
+  </si>
+  <si>
+    <t>0|0</t>
+  </si>
+  <si>
+    <t>떡만 있을 때 EncounterGroup 복귀 즉시 표시. 예 선택 시 산군 공격/피 효과/YOU DIE 후 재시도 선택지로 이동.</t>
+  </si>
+  <si>
+    <t>완성한 꿀떡을 산군에게 주시겠습니까?</t>
+  </si>
+  <si>
+    <t>CompleteQuest|Close</t>
+  </si>
+  <si>
+    <t>character_Sangun_04|</t>
+  </si>
+  <si>
+    <t>Stage3__Quest_01|</t>
+  </si>
+  <si>
+    <t>꿀떡이 있을 때 EncounterGroup 복귀 즉시 표시. 예 선택 시 꿀떡을 소비하고 Stage3 퀘스트 완료 처리.</t>
+  </si>
+  <si>
+    <t>Choice_Stage3_SungunQuest_04</t>
+  </si>
+  <si>
+    <t>전 장면으로 돌아가겠습니까?</t>
+  </si>
+  <si>
+    <t>ReturnPrevious|LoadGroup</t>
+  </si>
+  <si>
+    <t>EncounterGroup|MainMenuGroup</t>
+  </si>
+  <si>
+    <t>YOU DIE 이후 표시. 예는 EncounterGroup 재시작, 아니오는 메인 메뉴 이동.</t>
+  </si>
+  <si>
+    <t>Choice_Stage3_SungunQuest_01</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>떡과 꿀을 조합해 꿀떡을 만드시겠습니까?</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Choice_Stage3_SungunQuest_03</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>꿀 없이 떡만 산군에게 주시겠습니까?</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="7">
     <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
-      <color rgb="FF000000"/>
-      <sz val="10"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="&quot;맑은 고딕&quot;"/>
+      <family val="3"/>
       <charset val="129"/>
-      <family val="3"/>
-      <color rgb="FF000000"/>
-      <sz val="10"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
-      <color rgb="FF000000"/>
-      <sz val="10"/>
     </font>
     <font>
-      <name val="돋움"/>
-      <charset val="129"/>
-      <family val="3"/>
-      <color rgb="FF000000"/>
+      <b/>
       <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <family val="2"/>
-      <b val="1"/>
-      <sz val="10"/>
     </font>
     <font>
-      <name val="Arial"/>
-      <family val="2"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="10"/>
+      <sz val="8"/>
+      <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
     <font>
-      <name val="돋움"/>
+      <sz val="10"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
       <charset val="129"/>
-      <family val="3"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="?? ??"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <sz val="10"/>
     </font>
   </fonts>
   <fills count="8">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -84,7 +278,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.7999511703848384"/>
+        <fgColor theme="7" tint="0.79995117038483843"/>
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
@@ -105,7 +299,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -151,116 +345,46 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="12">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -412,598 +536,380 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:N8"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="17" defaultRowHeight="12.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:N1000"/>
+  <sheetFormatPr defaultColWidth="17" defaultRowHeight="12.5"/>
   <cols>
-    <col width="28.7265625" customWidth="1" style="1" min="1" max="1"/>
-    <col width="23.7265625" customWidth="1" style="1" min="2" max="2"/>
-    <col width="53.7265625" customWidth="1" min="3" max="3"/>
-    <col width="13.7265625" customWidth="1" min="4" max="4"/>
-    <col width="13.7265625" customWidth="1" style="1" min="5" max="5"/>
-    <col width="23.7265625" customWidth="1" style="1" min="6" max="7"/>
-    <col width="23.7265625" customWidth="1" min="8" max="13"/>
-    <col width="52.453125" customWidth="1" min="14" max="14"/>
+    <col min="1" max="1" width="28.7265625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="23.7265625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="53.7265625" customWidth="1"/>
+    <col min="4" max="4" width="13.7265625" customWidth="1"/>
+    <col min="5" max="5" width="13.7265625" style="1" customWidth="1"/>
+    <col min="6" max="7" width="23.7265625" style="1" customWidth="1"/>
+    <col min="8" max="13" width="23.7265625" customWidth="1"/>
+    <col min="14" max="14" width="52.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="31.5" customHeight="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>선택지 ID</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>화자 캐릭터 ID</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>질문 문장</t>
-        </is>
-      </c>
-      <c r="D1" s="4" t="inlineStr">
-        <is>
-          <t>선택 방식</t>
-        </is>
-      </c>
-      <c r="E1" s="4" t="inlineStr">
-        <is>
-          <t>선택지 개수</t>
-        </is>
-      </c>
-      <c r="F1" s="4" t="inlineStr">
-        <is>
-          <t>입력 키 목록(| 구분)</t>
-        </is>
-      </c>
-      <c r="G1" s="4" t="inlineStr">
-        <is>
-          <t>선택지 표시 문구 목록(| 구분)</t>
-        </is>
-      </c>
-      <c r="H1" s="4" t="inlineStr">
-        <is>
-          <t>결과 타입 목록(| 구분)</t>
-        </is>
-      </c>
-      <c r="I1" s="4" t="inlineStr">
-        <is>
-          <t>결과 값 목록(| 구분)</t>
-        </is>
-      </c>
-      <c r="J1" s="4" t="inlineStr">
-        <is>
-          <t>결과 수량 목록(| 구분)</t>
-        </is>
-      </c>
-      <c r="K1" s="4" t="inlineStr">
-        <is>
-          <t>다음 대사 ID 목록(| 구분)</t>
-        </is>
-      </c>
-      <c r="L1" s="4" t="inlineStr">
-        <is>
-          <t>다음 선택지 ID 목록(| 구분)</t>
-        </is>
-      </c>
-      <c r="M1" s="4" t="inlineStr">
-        <is>
-          <t>갱신 퀘스트 ID 목록(| 구분)</t>
-        </is>
-      </c>
-      <c r="N1" s="4" t="inlineStr">
-        <is>
-          <t>메모</t>
-        </is>
+    <row r="1" spans="1:14" ht="31.5" customHeight="1">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
-    <row r="2" ht="31.5" customHeight="1">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="B2" s="5" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="C2" s="5" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D2" s="5" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E2" s="5" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="F2" s="5" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="G2" s="6" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="H2" s="6" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="I2" s="7" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="J2" s="7" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="K2" s="7" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="L2" s="7" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="M2" s="7" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="N2" s="7" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
+    <row r="2" spans="1:14" ht="31.5" customHeight="1">
+      <c r="A2" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="K2" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="M2" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="N2" s="6" t="s">
+        <v>14</v>
       </c>
     </row>
-    <row r="3" ht="31.5" customFormat="1" customHeight="1" s="3">
-      <c r="A3" s="8" t="inlineStr">
-        <is>
-          <t>Id</t>
-        </is>
-      </c>
-      <c r="B3" s="8" t="inlineStr">
-        <is>
-          <t>SpeakerId</t>
-        </is>
-      </c>
-      <c r="C3" s="8" t="inlineStr">
-        <is>
-          <t>PromptText</t>
-        </is>
-      </c>
-      <c r="D3" s="8" t="inlineStr">
-        <is>
-          <t>ChoiceMode</t>
-        </is>
-      </c>
-      <c r="E3" s="8" t="inlineStr">
-        <is>
-          <t>OptionCount</t>
-        </is>
-      </c>
-      <c r="F3" s="8" t="inlineStr">
-        <is>
-          <t>OptionKeyList</t>
-        </is>
-      </c>
-      <c r="G3" s="8" t="inlineStr">
-        <is>
-          <t>OptionTextList</t>
-        </is>
-      </c>
-      <c r="H3" s="8" t="inlineStr">
-        <is>
-          <t>ResultTypeList</t>
-        </is>
-      </c>
-      <c r="I3" s="9" t="inlineStr">
-        <is>
-          <t>ResultValueList</t>
-        </is>
-      </c>
-      <c r="J3" s="9" t="inlineStr">
-        <is>
-          <t>ResultCountList</t>
-        </is>
-      </c>
-      <c r="K3" s="9" t="inlineStr">
-        <is>
-          <t>NextDialogueIdList</t>
-        </is>
-      </c>
-      <c r="L3" s="9" t="inlineStr">
-        <is>
-          <t>NextChoiceIdList</t>
-        </is>
-      </c>
-      <c r="M3" s="9" t="inlineStr">
-        <is>
-          <t>StageQuestIdList</t>
-        </is>
-      </c>
-      <c r="N3" s="9" t="inlineStr">
-        <is>
-          <t>Memo</t>
-        </is>
+    <row r="3" spans="1:14" s="2" customFormat="1" ht="31.5" customHeight="1">
+      <c r="A3" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="J3" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="K3" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="M3" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="N3" s="8" t="s">
+        <v>29</v>
       </c>
     </row>
-    <row r="4" ht="31.5" customHeight="1">
-      <c r="A4" s="11" t="inlineStr">
-        <is>
-          <t>Choice_Stage1_CartPumpkin_01</t>
-        </is>
-      </c>
-      <c r="B4" s="11" t="inlineStr">
-        <is>
-          <t>character_narrator_01</t>
-        </is>
-      </c>
-      <c r="C4" s="11" t="inlineStr">
-        <is>
-          <t>탐관오리처럼 탐욕스럽게 생긴 호박들입니다. 호박을 수확하시겠습니까?</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>YesNo</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
+    <row r="4" spans="1:14" ht="31.5" customHeight="1">
+      <c r="A4" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E4">
         <v>2</v>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Y|N</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>예|아니오</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>AddItem|Close</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Ing_Pumpkin_01|</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>10|0</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>|</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>|</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>Stage1_Quest_03|</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Stage1 Cart choice data</t>
-        </is>
+      <c r="F4" t="s">
+        <v>34</v>
+      </c>
+      <c r="G4" t="s">
+        <v>35</v>
+      </c>
+      <c r="H4" t="s">
+        <v>36</v>
+      </c>
+      <c r="I4" t="s">
+        <v>37</v>
+      </c>
+      <c r="J4" t="s">
+        <v>38</v>
+      </c>
+      <c r="K4" t="s">
+        <v>39</v>
+      </c>
+      <c r="L4" t="s">
+        <v>39</v>
+      </c>
+      <c r="M4" t="s">
+        <v>40</v>
+      </c>
+      <c r="N4" t="s">
+        <v>41</v>
       </c>
     </row>
-    <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="14" t="inlineStr">
-        <is>
-          <t>Choice_Stage3_SungunQuest_01</t>
-        </is>
-      </c>
-      <c r="B5" s="14" t="inlineStr">
-        <is>
-          <t>character_narrator_01</t>
-        </is>
-      </c>
-      <c r="C5" s="15" t="inlineStr">
-        <is>
-          <t>떡과 꿀을 조합해 꿀떡을 만드시겠습니까?</t>
-        </is>
-      </c>
-      <c r="D5" s="15" t="inlineStr">
-        <is>
-          <t>YesNo</t>
-        </is>
-      </c>
-      <c r="E5" s="14" t="n">
+    <row r="5" spans="1:14" ht="15.75" customHeight="1">
+      <c r="A5" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="E5" s="10">
         <v>2</v>
       </c>
-      <c r="F5" s="14" t="inlineStr">
-        <is>
-          <t>Y|N</t>
-        </is>
-      </c>
-      <c r="G5" s="15" t="inlineStr">
-        <is>
-          <t>예|아니오</t>
-        </is>
-      </c>
-      <c r="H5" s="15" t="inlineStr">
-        <is>
-          <t>MakeItem|Close</t>
-        </is>
-      </c>
-      <c r="I5" s="15" t="inlineStr">
-        <is>
-          <t>OO_HoneyKoreanCake_1|</t>
-        </is>
-      </c>
-      <c r="J5" s="15" t="inlineStr">
-        <is>
-          <t>1|0</t>
-        </is>
-      </c>
-      <c r="K5" s="15" t="inlineStr">
-        <is>
-          <t>|</t>
-        </is>
-      </c>
-      <c r="L5" s="15" t="inlineStr">
-        <is>
-          <t>|</t>
-        </is>
-      </c>
-      <c r="M5" s="15" t="inlineStr">
-        <is>
-          <t>|</t>
-        </is>
-      </c>
-      <c r="N5" s="15" t="inlineStr">
-        <is>
-          <t>필요 재료: OO_KoreanCake_1 1개 + Ing_Honey_01 1개. 예 선택 시 재료를 소비하고 꿀떡 1개를 추가한다.</t>
-        </is>
+      <c r="F5" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G5" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="H5" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="I5" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="J5" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="K5" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="L5" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="M5" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="N5" s="11" t="s">
+        <v>45</v>
       </c>
     </row>
-    <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="14" t="inlineStr">
-        <is>
-          <t>Choice_Stage3_SungunQuest_02</t>
-        </is>
-      </c>
-      <c r="B6" s="14" t="inlineStr">
-        <is>
-          <t>character_narrator_01</t>
-        </is>
-      </c>
-      <c r="C6" s="15" t="inlineStr">
-        <is>
-          <t>꿀 없이 떡만 산군에게 주시겠습니까?</t>
-        </is>
-      </c>
-      <c r="D6" s="15" t="inlineStr">
-        <is>
-          <t>YesNo</t>
-        </is>
-      </c>
-      <c r="E6" s="15" t="n">
+    <row r="6" spans="1:14" ht="15.75" customHeight="1">
+      <c r="A6" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="E6" s="11">
         <v>2</v>
       </c>
-      <c r="F6" s="15" t="inlineStr">
-        <is>
-          <t>Y|N</t>
-        </is>
-      </c>
-      <c r="G6" s="15" t="inlineStr">
-        <is>
-          <t>예|아니오</t>
-        </is>
-      </c>
-      <c r="H6" s="15" t="inlineStr">
-        <is>
-          <t>BadEnd|Close</t>
-        </is>
-      </c>
-      <c r="I6" s="15" t="inlineStr">
-        <is>
-          <t>Choice_Stage3_SungunQuest_04|</t>
-        </is>
-      </c>
-      <c r="J6" s="15" t="inlineStr">
-        <is>
-          <t>0|0</t>
-        </is>
-      </c>
-      <c r="K6" s="15" t="inlineStr">
-        <is>
-          <t>|</t>
-        </is>
-      </c>
-      <c r="L6" s="15" t="inlineStr">
-        <is>
-          <t>Choice_Stage3_SungunQuest_04|</t>
-        </is>
-      </c>
-      <c r="M6" s="15" t="inlineStr">
-        <is>
-          <t>|</t>
-        </is>
-      </c>
-      <c r="N6" s="15" t="inlineStr">
-        <is>
-          <t>떡만 있을 때 EncounterGroup 복귀 즉시 표시. 예 선택 시 산군 공격/피 효과/YOU DIE 후 재시도 선택지로 이동.</t>
-        </is>
+      <c r="F6" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="G6" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="H6" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="I6" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="J6" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="K6" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="L6" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="M6" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="N6" s="11" t="s">
+        <v>50</v>
       </c>
     </row>
-    <row r="7" ht="15.75" customHeight="1">
-      <c r="A7" s="14" t="inlineStr">
-        <is>
-          <t>Choice_Stage3_SungunQuest_03</t>
-        </is>
-      </c>
-      <c r="B7" s="14" t="inlineStr">
-        <is>
-          <t>character_narrator_01</t>
-        </is>
-      </c>
-      <c r="C7" s="15" t="inlineStr">
-        <is>
-          <t>완성한 꿀떡을 산군에게 주시겠습니까?</t>
-        </is>
-      </c>
-      <c r="D7" s="15" t="inlineStr">
-        <is>
-          <t>YesNo</t>
-        </is>
-      </c>
-      <c r="E7" s="15" t="n">
+    <row r="7" spans="1:14" ht="15.75" customHeight="1">
+      <c r="A7" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="E7" s="11">
         <v>2</v>
       </c>
-      <c r="F7" s="15" t="inlineStr">
-        <is>
-          <t>Y|N</t>
-        </is>
-      </c>
-      <c r="G7" s="15" t="inlineStr">
-        <is>
-          <t>예|아니오</t>
-        </is>
-      </c>
-      <c r="H7" s="15" t="inlineStr">
-        <is>
-          <t>CompleteQuest|Close</t>
-        </is>
-      </c>
-      <c r="I7" s="15" t="inlineStr">
-        <is>
-          <t>OO_HoneyKoreanCake_1|</t>
-        </is>
-      </c>
-      <c r="J7" s="15" t="inlineStr">
-        <is>
-          <t>1|0</t>
-        </is>
-      </c>
-      <c r="K7" s="15" t="inlineStr">
-        <is>
-          <t>character_Sangun_04|</t>
-        </is>
-      </c>
-      <c r="L7" s="15" t="inlineStr">
-        <is>
-          <t>|</t>
-        </is>
-      </c>
-      <c r="M7" s="15" t="inlineStr">
-        <is>
-          <t>Stage3__Quest_01|</t>
-        </is>
-      </c>
-      <c r="N7" s="15" t="inlineStr">
-        <is>
-          <t>꿀떡이 있을 때 EncounterGroup 복귀 즉시 표시. 예 선택 시 꿀떡을 소비하고 Stage3 퀘스트 완료 처리.</t>
-        </is>
+      <c r="F7" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="G7" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="H7" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="I7" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="J7" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="K7" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="L7" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="M7" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="N7" s="11" t="s">
+        <v>55</v>
       </c>
     </row>
-    <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="14" t="inlineStr">
-        <is>
-          <t>Choice_Stage3_SungunQuest_04</t>
-        </is>
-      </c>
-      <c r="B8" s="14" t="inlineStr">
-        <is>
-          <t>character_narrator_01</t>
-        </is>
-      </c>
-      <c r="C8" s="15" t="inlineStr">
-        <is>
-          <t>전 장면으로 돌아가겠습니까?</t>
-        </is>
-      </c>
-      <c r="D8" s="15" t="inlineStr">
-        <is>
-          <t>YesNo</t>
-        </is>
-      </c>
-      <c r="E8" s="15" t="n">
+    <row r="8" spans="1:14" ht="15.75" customHeight="1">
+      <c r="A8" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="E8" s="11">
         <v>2</v>
       </c>
-      <c r="F8" s="15" t="inlineStr">
-        <is>
-          <t>Y|N</t>
-        </is>
-      </c>
-      <c r="G8" s="15" t="inlineStr">
-        <is>
-          <t>예|아니오</t>
-        </is>
-      </c>
-      <c r="H8" s="15" t="inlineStr">
-        <is>
-          <t>ReturnPrevious|LoadGroup</t>
-        </is>
-      </c>
-      <c r="I8" s="15" t="inlineStr">
-        <is>
-          <t>EncounterGroup|MainMenuGroup</t>
-        </is>
-      </c>
-      <c r="J8" s="15" t="inlineStr">
-        <is>
-          <t>0|0</t>
-        </is>
-      </c>
-      <c r="K8" s="15" t="inlineStr">
-        <is>
-          <t>|</t>
-        </is>
-      </c>
-      <c r="L8" s="15" t="inlineStr">
-        <is>
-          <t>|</t>
-        </is>
-      </c>
-      <c r="M8" s="15" t="inlineStr">
-        <is>
-          <t>|</t>
-        </is>
-      </c>
-      <c r="N8" s="15" t="inlineStr">
-        <is>
-          <t>YOU DIE 이후 표시. 예는 EncounterGroup 재시작, 아니오는 메인 메뉴 이동.</t>
-        </is>
+      <c r="F8" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="G8" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="H8" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="I8" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="J8" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="K8" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="L8" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="M8" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="N8" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
-    <row r="9" ht="15.75" customHeight="1"/>
-    <row r="10" ht="15.75" customHeight="1"/>
-    <row r="11" ht="15.75" customHeight="1"/>
-    <row r="12" ht="15.75" customHeight="1"/>
-    <row r="13" ht="15.75" customHeight="1"/>
-    <row r="14" ht="15.75" customHeight="1"/>
-    <row r="15" ht="15.75" customHeight="1"/>
-    <row r="16" ht="15.75" customHeight="1"/>
+    <row r="9" spans="1:14" ht="15.75" customHeight="1"/>
+    <row r="10" spans="1:14" ht="15.75" customHeight="1"/>
+    <row r="11" spans="1:14" ht="15.75" customHeight="1"/>
+    <row r="12" spans="1:14" ht="15.75" customHeight="1"/>
+    <row r="13" spans="1:14" ht="15.75" customHeight="1"/>
+    <row r="14" spans="1:14" ht="15.75" customHeight="1"/>
+    <row r="15" spans="1:14" ht="15.75" customHeight="1"/>
+    <row r="16" spans="1:14" ht="15.75" customHeight="1"/>
     <row r="17" ht="15.75" customHeight="1"/>
     <row r="18" ht="15.75" customHeight="1"/>
     <row r="19" ht="15.75" customHeight="1"/>
@@ -1989,6 +1895,7 @@
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/JsonConverter/ExcelFiles/OO_Choice.xlsx
+++ b/JsonConverter/ExcelFiles/OO_Choice.xlsx
@@ -154,9 +154,6 @@
     <t>필요 재료: OO_KoreanCake_1 1개 + Ing_Honey_01 1개. 예 선택 시 재료를 소비하고 꿀떡 1개를 추가한다.</t>
   </si>
   <si>
-    <t>Choice_Stage3_SungunQuest_02</t>
-  </si>
-  <si>
     <t>BadEnd|Close</t>
   </si>
   <si>
@@ -167,9 +164,6 @@
   </si>
   <si>
     <t>떡만 있을 때 EncounterGroup 복귀 즉시 표시. 예 선택 시 산군 공격/피 효과/YOU DIE 후 재시도 선택지로 이동.</t>
-  </si>
-  <si>
-    <t>완성한 꿀떡을 산군에게 주시겠습니까?</t>
   </si>
   <si>
     <t>CompleteQuest|Close</t>
@@ -207,11 +201,19 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
+    <t>완성한 꿀떡을 산군에게 주시겠습니까?</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
     <t>Choice_Stage3_SungunQuest_03</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>꿀 없이 떡만 산군에게 주시겠습니까?</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Choice_Stage3_SungunQuest_02</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -728,13 +730,13 @@
     </row>
     <row r="5" spans="1:14" ht="15.75" customHeight="1">
       <c r="A5" s="10" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B5" s="10" t="s">
         <v>31</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D5" s="11" t="s">
         <v>33</v>
@@ -772,13 +774,13 @@
     </row>
     <row r="6" spans="1:14" ht="15.75" customHeight="1">
       <c r="A6" s="10" t="s">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="B6" s="10" t="s">
         <v>31</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D6" s="11" t="s">
         <v>33</v>
@@ -793,36 +795,36 @@
         <v>35</v>
       </c>
       <c r="H6" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="I6" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="I6" s="11" t="s">
+      <c r="J6" s="11" t="s">
         <v>48</v>
-      </c>
-      <c r="J6" s="11" t="s">
-        <v>49</v>
       </c>
       <c r="K6" s="11" t="s">
         <v>39</v>
       </c>
       <c r="L6" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="M6" s="11" t="s">
         <v>39</v>
       </c>
       <c r="N6" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="15.75" customHeight="1">
       <c r="A7" s="10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B7" s="10" t="s">
         <v>31</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="D7" s="11" t="s">
         <v>33</v>
@@ -837,7 +839,7 @@
         <v>35</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="I7" s="11" t="s">
         <v>43</v>
@@ -846,27 +848,27 @@
         <v>44</v>
       </c>
       <c r="K7" s="11" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="L7" s="11" t="s">
         <v>39</v>
       </c>
       <c r="M7" s="11" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="N7" s="11" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="15.75" customHeight="1">
       <c r="A8" s="10" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B8" s="10" t="s">
         <v>31</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D8" s="11" t="s">
         <v>33</v>
@@ -881,13 +883,13 @@
         <v>35</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="I8" s="11" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="J8" s="11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="K8" s="11" t="s">
         <v>39</v>
@@ -899,7 +901,7 @@
         <v>39</v>
       </c>
       <c r="N8" s="11" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="15.75" customHeight="1"/>
@@ -1897,5 +1899,6 @@
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/JsonConverter/ExcelFiles/OO_Choice.xlsx
+++ b/JsonConverter/ExcelFiles/OO_Choice.xlsx
@@ -106,9 +106,6 @@
     <t>Memo</t>
   </si>
   <si>
-    <t>Choice_Stage1_CartPumpkin_01</t>
-  </si>
-  <si>
     <t>character_narrator_01</t>
   </si>
   <si>
@@ -214,6 +211,10 @@
   </si>
   <si>
     <t>Choice_Stage3_SungunQuest_02</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Choice_Stage1_CartPumpkin_01</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -686,222 +687,222 @@
     </row>
     <row r="4" spans="1:14" ht="31.5" customHeight="1">
       <c r="A4" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="B4" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="C4" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="D4" t="s">
         <v>32</v>
-      </c>
-      <c r="D4" t="s">
-        <v>33</v>
       </c>
       <c r="E4">
         <v>2</v>
       </c>
       <c r="F4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G4" t="s">
         <v>34</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>35</v>
       </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
         <v>36</v>
       </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
         <v>37</v>
       </c>
-      <c r="J4" t="s">
+      <c r="K4" t="s">
         <v>38</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
+        <v>38</v>
+      </c>
+      <c r="M4" t="s">
         <v>39</v>
       </c>
-      <c r="L4" t="s">
-        <v>39</v>
-      </c>
-      <c r="M4" t="s">
+      <c r="N4" t="s">
         <v>40</v>
-      </c>
-      <c r="N4" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="15.75" customHeight="1">
       <c r="A5" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="B5" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>60</v>
-      </c>
       <c r="D5" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E5" s="10">
         <v>2</v>
       </c>
       <c r="F5" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="G5" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="G5" s="11" t="s">
-        <v>35</v>
-      </c>
       <c r="H5" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="I5" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="I5" s="11" t="s">
+      <c r="J5" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="J5" s="11" t="s">
+      <c r="K5" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="L5" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="M5" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="N5" s="11" t="s">
         <v>44</v>
-      </c>
-      <c r="K5" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="L5" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="M5" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="N5" s="11" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="15.75" customHeight="1">
       <c r="A6" s="10" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E6" s="11">
         <v>2</v>
       </c>
       <c r="F6" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="G6" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="G6" s="11" t="s">
-        <v>35</v>
-      </c>
       <c r="H6" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="I6" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="I6" s="11" t="s">
+      <c r="J6" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="J6" s="11" t="s">
+      <c r="K6" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="L6" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="M6" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="N6" s="11" t="s">
         <v>48</v>
-      </c>
-      <c r="K6" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="L6" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="M6" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="N6" s="11" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="15.75" customHeight="1">
       <c r="A7" s="10" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E7" s="11">
         <v>2</v>
       </c>
       <c r="F7" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="G7" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="G7" s="11" t="s">
-        <v>35</v>
-      </c>
       <c r="H7" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="I7" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="J7" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="K7" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="I7" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="J7" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="K7" s="11" t="s">
+      <c r="L7" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="M7" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="L7" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="M7" s="11" t="s">
+      <c r="N7" s="11" t="s">
         <v>52</v>
-      </c>
-      <c r="N7" s="11" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="15.75" customHeight="1">
       <c r="A8" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="B8" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>55</v>
-      </c>
       <c r="D8" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E8" s="11">
         <v>2</v>
       </c>
       <c r="F8" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="G8" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="G8" s="11" t="s">
-        <v>35</v>
-      </c>
       <c r="H8" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="I8" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="I8" s="11" t="s">
+      <c r="J8" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="K8" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="L8" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="M8" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="N8" s="11" t="s">
         <v>57</v>
-      </c>
-      <c r="J8" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="K8" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="L8" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="M8" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="N8" s="11" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="15.75" customHeight="1"/>
